--- a/docentes/Flores González Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Flores González Ángel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -68,6 +68,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>YOLET</t>
   </si>
 </sst>
 </file>
@@ -692,7 +701,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -722,6 +731,29 @@
         <v>16</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920007</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Flores González Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Flores González Ángel - Estadisticos 20221.xlsx
@@ -70,13 +70,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>COBOS</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
-    <t>YOLET</t>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
   </si>
 </sst>
 </file>
@@ -477,10 +477,10 @@
         <v>44</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>2</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>42</v>
@@ -489,7 +489,7 @@
         <v>95.45</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -500,7 +500,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -509,10 +509,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>91.43000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="H3">
         <v>8.4</v>
@@ -571,7 +571,7 @@
         <v>44</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -588,13 +588,13 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -653,10 +653,10 @@
         <v>44</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>2</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>42</v>
@@ -665,7 +665,7 @@
         <v>95.45</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -676,7 +676,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -685,10 +685,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>91.43000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="H3">
         <v>8.4</v>
@@ -733,7 +733,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920007</v>
+        <v>20330051920089</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>

--- a/docentes/Flores González Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Flores González Ángel - Estadisticos 20221.xlsx
@@ -568,16 +568,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>95.45</v>
+      </c>
+      <c r="H2">
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/docentes/Flores González Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Flores González Ángel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -70,10 +70,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>MIXCOHA</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
@@ -594,16 +603,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H3">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -685,16 +697,16 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>91.67</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -704,7 +716,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -736,16 +748,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920089</v>
+        <v>21330051920195</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -754,6 +766,29 @@
         <v>10</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920089</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Flores González Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Flores González Ángel - Estadisticos 20221.xlsx
@@ -512,10 +512,10 @@
         <v>36</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>3</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>33</v>
@@ -524,7 +524,7 @@
         <v>91.67</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -603,10 +603,10 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>30</v>
@@ -615,7 +615,7 @@
         <v>83.33</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -694,10 +694,10 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>30</v>
@@ -706,7 +706,7 @@
         <v>83.33</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Flores González Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Flores González Ángel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -70,22 +70,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>DE JESUS</t>
   </si>
   <si>
     <t>MIXCOHA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>NAZARIO</t>
   </si>
   <si>
     <t>EVARISTO</t>
   </si>
   <si>
-    <t>LUIS ENRIQUE</t>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
   </si>
 </sst>
 </file>
@@ -697,16 +706,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>69.44</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -716,7 +725,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -748,16 +757,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920195</v>
+        <v>20330051920018</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -777,10 +786,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -790,6 +799,29 @@
       </c>
       <c r="G3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920019</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Flores González Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Flores González Ángel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -70,28 +70,37 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
     <t>NAZARIO</t>
   </si>
   <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
     <t>ENRIQUEZ</t>
   </si>
   <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
     <t>EDGAR</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
   </si>
   <si>
     <t>ABRIL</t>
@@ -725,7 +734,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -757,16 +766,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920018</v>
+        <v>20330051920089</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -780,16 +789,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920089</v>
+        <v>21330051920393</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -803,16 +812,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920019</v>
+        <v>20330051920018</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -821,6 +830,29 @@
         <v>10</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920019</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Flores González Ángel - Estadisticos 20221.xlsx
+++ b/docentes/Flores González Ángel - Estadisticos 20221.xlsx
@@ -698,7 +698,7 @@
         <v>95.45</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
